--- a/apps/admin-web/public/templates/price-card-import-template-PPT-1.xlsx
+++ b/apps/admin-web/public/templates/price-card-import-template-PPT-1.xlsx
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">期望的类别值；ZONE、ADDRESS_TYPE、SERVICE_OPTION 来源必填</t>
+          <t xml:space="preserve">期望的类别值；ZONE、ADDRESS_TYPE、SERVICE_OPTION 来源必填，ADDRESS_NATURE 来源必填且只收 COMMERCIAL、RESIDENTIAL</t>
         </is>
       </c>
     </row>

--- a/apps/admin-web/public/templates/price-card-import-template-PPT-1.xlsx
+++ b/apps/admin-web/public/templates/price-card-import-template-PPT-1.xlsx
@@ -2261,7 +2261,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定的特征来源；PREDICATE 必填</t>
+          <t xml:space="preserve">判定的特征来源；PREDICATE 必填。CHARGEABLE_WEIGHT 是包裹自身的计价重量（派生、进位之后），不含条件最低计价重量的抬高</t>
         </is>
       </c>
     </row>
